--- a/outputs/Block6C_Electoral_Risk.xlsx
+++ b/outputs/Block6C_Electoral_Risk.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Component</t>
   </si>
@@ -34,7 +34,10 @@
     <t>Popular Vote</t>
   </si>
   <si>
-    <t>Competitive</t>
+    <t>Favored</t>
+  </si>
+  <si>
+    <t>Very Competitive</t>
   </si>
   <si>
     <t>Range-Based Estimate</t>
@@ -426,7 +429,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -434,10 +437,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -445,10 +448,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Electoral_Risk.xlsx
+++ b/outputs/Block6C_Electoral_Risk.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Component</t>
   </si>
@@ -34,19 +34,16 @@
     <t>Popular Vote</t>
   </si>
   <si>
-    <t>Favored</t>
-  </si>
-  <si>
-    <t>Very Competitive</t>
+    <t>Competitive</t>
   </si>
   <si>
     <t>Range-Based Estimate</t>
   </si>
   <si>
-    <t>Derived only from the same 435 district simulations; joint-mode central and joint distribution centers are reported separately.</t>
-  </si>
-  <si>
-    <t>Derived only from the same 11 monitored state-race simulations plus fixed seats; margin sensitivity is audited.</t>
+    <t>Derived from the same 50,000 complete 435-district simulations; race-first central and joint distribution statistics are reported separately.</t>
+  </si>
+  <si>
+    <t>Derived from the unified 35-race Senate simulation: 12 monitored races plus 23 structural-only races and 65 fixed non-up seats; margin sensitivity is audited.</t>
   </si>
   <si>
     <t>Based only on simulated popular vote uncertainty.</t>
@@ -429,7 +426,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -437,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -448,10 +445,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Electoral_Risk.xlsx
+++ b/outputs/Block6C_Electoral_Risk.xlsx
@@ -43,7 +43,7 @@
     <t>Derived from the same 50,000 complete 435-district simulations; race-first central and joint distribution statistics are reported separately.</t>
   </si>
   <si>
-    <t>Derived from the unified 35-race Senate simulation: 12 monitored races plus 23 structural-only races and 65 fixed non-up seats; margin sensitivity is audited.</t>
+    <t>Derived from the unified 35-race Senate simulation: 15 monitored races plus 20 structural-only races and 65 fixed non-up seats; margin sensitivity is audited.</t>
   </si>
   <si>
     <t>Based only on simulated popular vote uncertainty.</t>
